--- a/artfynd/A 14895-2026 artfynd.xlsx
+++ b/artfynd/A 14895-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67125200</v>
+        <v>67125249</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539693.1891157295</v>
+        <v>539704</v>
       </c>
       <c r="R2" t="n">
-        <v>7233355.212938461</v>
+        <v>7233306</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,17 +769,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,37 +797,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67125251</v>
+        <v>67125186</v>
       </c>
       <c r="B3" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>67</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538749.0729858186</v>
+        <v>539053</v>
       </c>
       <c r="R3" t="n">
-        <v>7233293.144567742</v>
+        <v>7233462</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,15 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67125221</v>
+        <v>67125209</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,39 +930,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538911.8084353256</v>
+        <v>538685</v>
       </c>
       <c r="R4" t="n">
-        <v>7233283.115525994</v>
+        <v>7233581</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,6 +1010,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1046,15 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67125209</v>
+        <v>67125210</v>
       </c>
       <c r="B5" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,12 +1061,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538684.7954342421</v>
+        <v>539040</v>
       </c>
       <c r="R5" t="n">
-        <v>7233581.017386243</v>
+        <v>7233472</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,15 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67125289</v>
+        <v>67125211</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,21 +1174,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1213,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539382.9559238753</v>
+        <v>539425</v>
       </c>
       <c r="R6" t="n">
-        <v>7233492.898199901</v>
+        <v>7233447</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1248,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1258,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,15 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>67125219</v>
+        <v>67125215</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,39 +1296,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538898.0673115898</v>
+        <v>539427</v>
       </c>
       <c r="R7" t="n">
-        <v>7233241.806600237</v>
+        <v>7233442</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1380,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1390,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,6 +1376,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1417,15 +1407,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>67125162</v>
+        <v>67125251</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,21 +1418,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1457,10 +1442,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539426.9118775141</v>
+        <v>538749</v>
       </c>
       <c r="R8" t="n">
-        <v>7233441.868948802</v>
+        <v>7233293</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1492,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1502,7 +1487,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1544,15 +1529,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67125211</v>
+        <v>67125252</v>
       </c>
       <c r="B9" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,21 +1540,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1584,10 +1564,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539425.1643299303</v>
+        <v>538777</v>
       </c>
       <c r="R9" t="n">
-        <v>7233446.881370268</v>
+        <v>7233408</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1619,7 +1599,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1629,7 +1609,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1671,37 +1651,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>67125249</v>
+        <v>67125253</v>
       </c>
       <c r="B10" t="n">
-        <v>89577</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>48</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1711,10 +1686,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539703.9372295054</v>
+        <v>539455</v>
       </c>
       <c r="R10" t="n">
-        <v>7233305.837080441</v>
+        <v>7233316</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1746,7 +1721,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1756,7 +1731,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1798,37 +1773,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>67125287</v>
+        <v>67125181</v>
       </c>
       <c r="B11" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>918</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1838,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539060.8865587915</v>
+        <v>539203</v>
       </c>
       <c r="R11" t="n">
-        <v>7233447.911930468</v>
+        <v>7233416</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1873,7 +1843,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1883,7 +1853,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1925,15 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>67125225</v>
+        <v>67125259</v>
       </c>
       <c r="B12" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,39 +1906,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539342.1203664577</v>
+        <v>539077</v>
       </c>
       <c r="R12" t="n">
-        <v>7233499.067706744</v>
+        <v>7233424</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2005,7 +1965,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2015,7 +1975,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2026,6 +1986,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2042,37 +2017,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>67125186</v>
+        <v>67125260</v>
       </c>
       <c r="B13" t="n">
-        <v>90079</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2082,10 +2052,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539053.1365256907</v>
+        <v>539322</v>
       </c>
       <c r="R13" t="n">
-        <v>7233462.077263935</v>
+        <v>7233491</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2117,7 +2087,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2127,7 +2097,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2169,15 +2139,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>67125161</v>
+        <v>67125156</v>
       </c>
       <c r="B14" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2209,10 +2174,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539423.8873063971</v>
+        <v>538704</v>
       </c>
       <c r="R14" t="n">
-        <v>7233448.123249947</v>
+        <v>7233298</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2244,7 +2209,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2254,7 +2219,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2296,37 +2261,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>67125243</v>
+        <v>67125159</v>
       </c>
       <c r="B15" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2336,10 +2296,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539688.9487921175</v>
+        <v>539053</v>
       </c>
       <c r="R15" t="n">
-        <v>7233358.093532748</v>
+        <v>7233462</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2371,7 +2331,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2381,7 +2341,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2395,17 +2355,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2423,37 +2383,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>67125189</v>
+        <v>67125160</v>
       </c>
       <c r="B16" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2463,10 +2418,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>538692.0298028535</v>
+        <v>539059</v>
       </c>
       <c r="R16" t="n">
-        <v>7233573.978605955</v>
+        <v>7233430</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2498,7 +2453,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2508,7 +2463,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2519,6 +2474,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2535,15 +2505,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>67125223</v>
+        <v>67125161</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,39 +2516,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>539215.1111670552</v>
+        <v>539424</v>
       </c>
       <c r="R17" t="n">
-        <v>7233413.867695331</v>
+        <v>7233448</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2615,7 +2575,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2625,7 +2585,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2636,6 +2596,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2652,15 +2627,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>67125288</v>
+        <v>67125162</v>
       </c>
       <c r="B18" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,21 +2638,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2692,10 +2662,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>539061.9377509534</v>
+        <v>539427</v>
       </c>
       <c r="R18" t="n">
-        <v>7233431.979273669</v>
+        <v>7233442</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2727,7 +2697,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2737,7 +2707,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2779,15 +2749,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>67125265</v>
+        <v>67125163</v>
       </c>
       <c r="B19" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2795,21 +2760,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2819,10 +2784,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>539077.1658724865</v>
+        <v>539424</v>
       </c>
       <c r="R19" t="n">
-        <v>7233424.20757546</v>
+        <v>7233415</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2854,7 +2819,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2864,7 +2829,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2906,15 +2871,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>67125270</v>
+        <v>67125164</v>
       </c>
       <c r="B20" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2922,21 +2882,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2946,10 +2906,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>539423.1424614011</v>
+        <v>539643</v>
       </c>
       <c r="R20" t="n">
-        <v>7233440.979291538</v>
+        <v>7233350</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2981,7 +2941,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2991,7 +2951,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3033,37 +2993,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>67125305</v>
+        <v>67125270</v>
       </c>
       <c r="B21" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3073,10 +3028,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>539213.0107992197</v>
+        <v>539423</v>
       </c>
       <c r="R21" t="n">
-        <v>7233413.839783779</v>
+        <v>7233441</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3108,7 +3063,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3118,7 +3073,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3132,17 +3087,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3160,15 +3115,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>67125260</v>
+        <v>67125148</v>
       </c>
       <c r="B22" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3176,21 +3126,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>1588</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3200,10 +3150,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>539322.0636450519</v>
+        <v>539360</v>
       </c>
       <c r="R22" t="n">
-        <v>7233490.827204968</v>
+        <v>7233486</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3235,7 +3185,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3245,7 +3195,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3287,37 +3237,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>67125163</v>
+        <v>67125275</v>
       </c>
       <c r="B23" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92283</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>2063</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3327,10 +3272,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>539423.9100739683</v>
+        <v>539015</v>
       </c>
       <c r="R23" t="n">
-        <v>7233414.971256949</v>
+        <v>7233457</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3362,7 +3307,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3372,7 +3317,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3414,37 +3359,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>67125181</v>
+        <v>67125200</v>
       </c>
       <c r="B24" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>918</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3454,10 +3394,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>539202.9011627662</v>
+        <v>539693</v>
       </c>
       <c r="R24" t="n">
-        <v>7233415.803712823</v>
+        <v>7233355</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3489,7 +3429,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3499,7 +3439,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3513,17 +3453,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3544,12 +3484,7 @@
         <v>67125227</v>
       </c>
       <c r="B25" t="n">
-        <v>89449</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92037</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3571,7 +3506,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3581,10 +3516,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538970.97628521</v>
+        <v>538971</v>
       </c>
       <c r="R25" t="n">
-        <v>7233416.088878703</v>
+        <v>7233416</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3653,55 +3588,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>67125224</v>
+        <v>67125150</v>
       </c>
       <c r="B26" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>539342.1534123621</v>
+        <v>538749</v>
       </c>
       <c r="R26" t="n">
-        <v>7233465.077159675</v>
+        <v>7233276</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3733,7 +3658,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3743,7 +3668,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3754,6 +3679,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3770,37 +3710,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>67125190</v>
+        <v>67125239</v>
       </c>
       <c r="B27" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3810,10 +3745,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>539312.1730257113</v>
+        <v>539681</v>
       </c>
       <c r="R27" t="n">
-        <v>7233507.900629503</v>
+        <v>7233350</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3845,7 +3780,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3855,7 +3790,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3866,6 +3801,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3882,37 +3832,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>67125253</v>
+        <v>67125185</v>
       </c>
       <c r="B28" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3922,10 +3867,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>539455.0648279467</v>
+        <v>539448</v>
       </c>
       <c r="R28" t="n">
-        <v>7233315.928512019</v>
+        <v>7233346</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3957,7 +3902,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3967,7 +3912,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3981,17 +3926,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4009,37 +3954,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>67125160</v>
+        <v>67125305</v>
       </c>
       <c r="B29" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4049,10 +3989,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>539059.0250228104</v>
+        <v>539213</v>
       </c>
       <c r="R29" t="n">
-        <v>7233429.842478561</v>
+        <v>7233414</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4084,7 +4024,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4094,7 +4034,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4108,17 +4048,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4136,37 +4076,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>67125239</v>
+        <v>67125242</v>
       </c>
       <c r="B30" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4176,10 +4111,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>539681.0744392868</v>
+        <v>539213</v>
       </c>
       <c r="R30" t="n">
-        <v>7233350.014070277</v>
+        <v>7233414</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4211,7 +4146,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4221,7 +4156,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4235,17 +4170,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4263,37 +4198,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>67125215</v>
+        <v>67125243</v>
       </c>
       <c r="B31" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4303,10 +4233,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>539426.9118775141</v>
+        <v>539689</v>
       </c>
       <c r="R31" t="n">
-        <v>7233441.868948802</v>
+        <v>7233358</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4338,7 +4268,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4348,7 +4278,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4362,17 +4292,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4390,50 +4320,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>67125159</v>
+        <v>67125301</v>
       </c>
       <c r="B32" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57825</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100096</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>539053.1365256907</v>
+        <v>538953</v>
       </c>
       <c r="R32" t="n">
-        <v>7233462.077263935</v>
+        <v>7233439</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4465,7 +4399,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4475,7 +4409,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4486,21 +4420,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4517,15 +4436,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>67125252</v>
+        <v>67125219</v>
       </c>
       <c r="B33" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4533,34 +4447,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>538776.9740993922</v>
+        <v>538898</v>
       </c>
       <c r="R33" t="n">
-        <v>7233408.077717987</v>
+        <v>7233242</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4592,7 +4511,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4602,7 +4521,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4613,21 +4532,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4644,50 +4548,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>67125242</v>
+        <v>67125220</v>
       </c>
       <c r="B34" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>539213.0107992197</v>
+        <v>538908</v>
       </c>
       <c r="R34" t="n">
-        <v>7233413.839783779</v>
+        <v>7233246</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4719,7 +4623,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4729,7 +4633,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4740,21 +4644,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4771,15 +4660,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>67125148</v>
+        <v>67125221</v>
       </c>
       <c r="B35" t="n">
-        <v>89557</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4787,34 +4671,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>539359.9420354925</v>
+        <v>538912</v>
       </c>
       <c r="R35" t="n">
-        <v>7233485.876879439</v>
+        <v>7233283</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4846,7 +4735,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4856,7 +4745,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4867,21 +4756,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4898,15 +4772,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>67125164</v>
+        <v>67125223</v>
       </c>
       <c r="B36" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4914,34 +4783,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>539642.841261154</v>
+        <v>539215</v>
       </c>
       <c r="R36" t="n">
-        <v>7233349.919866278</v>
+        <v>7233414</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4973,7 +4847,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4983,7 +4857,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4994,21 +4868,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5025,15 +4884,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>67125210</v>
+        <v>67125224</v>
       </c>
       <c r="B37" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5041,34 +4895,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>539039.9812359104</v>
+        <v>539342</v>
       </c>
       <c r="R37" t="n">
-        <v>7233471.974613032</v>
+        <v>7233465</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5100,7 +4959,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5110,7 +4969,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5121,21 +4980,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5152,50 +4996,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>67125185</v>
+        <v>67125225</v>
       </c>
       <c r="B38" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539447.9395811376</v>
+        <v>539342</v>
       </c>
       <c r="R38" t="n">
-        <v>7233346.049042329</v>
+        <v>7233499</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5227,7 +5071,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5237,7 +5081,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5248,21 +5092,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5279,50 +5108,59 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>67125275</v>
+        <v>67125175</v>
       </c>
       <c r="B39" t="n">
-        <v>89734</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2063</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539014.9714806824</v>
+        <v>539449</v>
       </c>
       <c r="R39" t="n">
-        <v>7233456.956330443</v>
+        <v>7233318</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5354,7 +5192,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5364,7 +5202,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5375,21 +5213,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5406,50 +5229,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>67125150</v>
+        <v>67125177</v>
       </c>
       <c r="B40" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Krutskogen, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>538748.878784671</v>
+        <v>538913</v>
       </c>
       <c r="R40" t="n">
-        <v>7233275.935655641</v>
+        <v>7233251</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5481,7 +5303,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5491,7 +5313,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5502,21 +5324,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5530,6 +5337,220 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>67125189</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Krutskogen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>538692</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7233574</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2017-08-06</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2017-08-06</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>67125190</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Krutskogen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>539312</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7233508</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2017-08-06</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2017-08-06</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
